--- a/files/tarot/TAROT_data.xlsx
+++ b/files/tarot/TAROT_data.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\GGD_MAGIA\GGD_DATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\tarot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06EE67E-6EEA-4213-8748-50FB520891B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{855E04F3-AE86-4387-9A8B-7A73EBB52A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="375" yWindow="750" windowWidth="27150" windowHeight="14415" xr2:uid="{12E5FF72-4590-4256-885D-534FFBE7C063}"/>
+    <workbookView xWindow="615" yWindow="780" windowWidth="27990" windowHeight="14415" xr2:uid="{12E5FF72-4590-4256-885D-534FFBE7C063}"/>
   </bookViews>
   <sheets>
     <sheet name="tarot" sheetId="2" r:id="rId1"/>
+    <sheet name="tarot (元データ)" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="129">
   <si>
     <t>愚者</t>
     <rPh sb="0" eb="2">
@@ -1206,6 +1207,519 @@
   </si>
   <si>
     <t>のなめ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>探索時の獲得報酬が増える、レア取得率が上がる</t>
+    <rPh sb="0" eb="3">
+      <t>タンサクジ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カクトク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ホウシュウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>シュトクリツ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前衛配置のキャラクタの攻撃力が20％UPし、被ダメージが20％増し(端数切上げ)になる</t>
+    <rPh sb="31" eb="32">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ハスウ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>キリア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキルの精神力消費が倍になり、威力や効果、継続時間も2倍になる</t>
+    <rPh sb="4" eb="7">
+      <t>セイシンリョク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="21" eb="25">
+      <t>ケイゾクジカン</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>戦闘毎にランダムで味方一人の攻撃力が50%上がる。</t>
+    <rPh sb="0" eb="2">
+      <t>セントウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ゴト</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前衛位置にいるキャラクタが一人の時、そのキャラの攻撃力が50％上がる。</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンエイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒトリ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="24" eb="27">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最も精神力の高いメンバーの最大値と同量のSPを得る。</t>
+    <rPh sb="0" eb="1">
+      <t>モット</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>セイシンリョク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>サイダイチ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ドウリョウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>エ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キャラクターが前衛配置の間、リロード時間が20%短縮される</t>
+    <rPh sb="7" eb="9">
+      <t>ゼンエイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>タンシュク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵が高レベルの場合、レベル差による攻撃力､命中率減少を半分にする。</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>コウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>メイチュウリツ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ゲンショウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ハンブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵が低レベルの場合、レベル差による攻撃力､命中率増加を倍にする。</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>テイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>メイチュウリツ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ゾウカ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全員の攻撃の命中率が10％上がる、距離による命中率マイナス補正を無くす。</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンイン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>メイチュウリツ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>メイチュウリツ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ホセイ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メンバーの平均レベルで1レベル上昇できる分のストック経験点を得る。</t>
+    <rPh sb="20" eb="21">
+      <t>ブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>戦闘突入ごとにメンバーの誰か生命力を最大値の10%失い、他の誰か一人の攻撃力が20%上がる。</t>
+    <rPh sb="0" eb="2">
+      <t>セントウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>トツニュウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ダレ</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>サイダイチ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ウシナ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ダレ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ヒトリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メンバー全員の最大生命力が最大の30%上がる。その分生命力を得る。</t>
+    <rPh sb="7" eb="9">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>セイメイリョク</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>エ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マップ上のいくつかの敵のレベルが1上がる。</t>
+    <rPh sb="3" eb="4">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メンバー全員の精神力を200増す。最大値を超えて保持される。</t>
+    <rPh sb="4" eb="6">
+      <t>ゼンイン</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>セイシンリョク</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>サイダイチ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ホジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>親愛度がプラスの場合、攻撃力が20％上がる</t>
+    <rPh sb="0" eb="2">
+      <t>シンアイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>戦闘毎にランダムで味方一人の攻撃力が50％上がり、1秒ごとに1点の生命力を失うようになる</t>
+    <rPh sb="14" eb="17">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="33" eb="36">
+      <t>セイメイリョク</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>ウシナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>戦闘時の獲得経験値が1.3倍になる</t>
+    <rPh sb="0" eb="3">
+      <t>セントウジ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カクトク</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>ケイケンチ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵のすべての攻撃速度、弾丸の速度、移動速度を20％遅くする</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>コウゲキソクド</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ダンガン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="17" eb="21">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>オソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マップ上に存在する魔女のどれか一つのレベルが1上がる</t>
+    <rPh sb="3" eb="4">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>マジョ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マップ上に存在する魔女のどれか一つのレベルが2上がる</t>
+    <rPh sb="3" eb="4">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>マジョ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>味方全員のクリティカルヒット率が5%、クリティカルヒット倍率が50%上がる</t>
+    <rPh sb="0" eb="2">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゼンイン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>バイリツ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マップ上の3つの敵のレベルが1上がる。</t>
+    <rPh sb="3" eb="4">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力が20%上がり、リロード時間が10%遅くなる</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>オソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>後衛位置にいるキャラクターの攻撃力が30%上がる。</t>
+    <rPh sb="0" eb="2">
+      <t>コウエイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前衛位置のキャラクタの攻撃力が20%上がる、後衛位置にのキャラクタの攻撃力が10%下がる</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンエイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>コウエイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="34" eb="37">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>サ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>戦闘後獲得するSPが1.5倍になる</t>
+    <rPh sb="0" eb="2">
+      <t>セントウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カクトク</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>バイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1213,7 +1727,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1235,6 +1749,14 @@
       <name val="MS UI Gothic"/>
       <family val="3"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1259,11 +1781,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1586,7 +2111,7 @@
     <col min="2" max="2" width="14.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.875" customWidth="1"/>
+    <col min="5" max="5" width="61.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.4">
@@ -1620,6 +2145,496 @@
       <c r="D2" s="1" t="s">
         <v>97</v>
       </c>
+      <c r="E2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E6" t="s">
+        <v>105</v>
+      </c>
+      <c r="F6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E7" t="s">
+        <v>107</v>
+      </c>
+      <c r="F7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E8" t="s">
+        <v>117</v>
+      </c>
+      <c r="F8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E9" t="s">
+        <v>108</v>
+      </c>
+      <c r="F9" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E10" t="s">
+        <v>109</v>
+      </c>
+      <c r="F10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E11" t="s">
+        <v>111</v>
+      </c>
+      <c r="F11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E12" t="s">
+        <v>112</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E13" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E15" t="s">
+        <v>123</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E18" t="s">
+        <v>45</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E19" t="s">
+        <v>35</v>
+      </c>
+      <c r="F19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E20" t="s">
+        <v>128</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F22" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47F4595F-511C-4045-92B3-3F63E9408AB1}">
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="61.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>97</v>
+      </c>
       <c r="E2" t="s">
         <v>3</v>
       </c>

--- a/files/tarot/TAROT_data.xlsx
+++ b/files/tarot/TAROT_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\tarot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{855E04F3-AE86-4387-9A8B-7A73EBB52A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D3BA1F-C381-4175-AD02-DF2E084E1595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="615" yWindow="780" windowWidth="27990" windowHeight="14415" xr2:uid="{12E5FF72-4590-4256-885D-534FFBE7C063}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="131">
   <si>
     <t>愚者</t>
     <rPh sb="0" eb="2">
@@ -1210,28 +1210,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>探索時の獲得報酬が増える、レア取得率が上がる</t>
-    <rPh sb="0" eb="3">
-      <t>タンサクジ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>カクトク</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ホウシュウ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>フ</t>
-    </rPh>
-    <rPh sb="15" eb="18">
-      <t>シュトクリツ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>ア</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>前衛配置のキャラクタの攻撃力が20％UPし、被ダメージが20％増し(端数切上げ)になる</t>
     <rPh sb="31" eb="32">
       <t>マ</t>
@@ -1318,25 +1296,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>キャラクターが前衛配置の間、リロード時間が20%短縮される</t>
-    <rPh sb="7" eb="9">
-      <t>ゼンエイ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ハイチ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>アイダ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ジカン</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>タンシュク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>敵が高レベルの場合、レベル差による攻撃力､命中率減少を半分にする。</t>
     <rPh sb="0" eb="1">
       <t>テキ</t>
@@ -1618,25 +1577,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>味方全員のクリティカルヒット率が5%、クリティカルヒット倍率が50%上がる</t>
-    <rPh sb="0" eb="2">
-      <t>ミカタ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ゼンイン</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>リツ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>バイリツ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>ア</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>マップ上の3つの敵のレベルが1上がる。</t>
     <rPh sb="3" eb="4">
       <t>ウエ</t>
@@ -1679,7 +1619,23 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>前衛位置のキャラクタの攻撃力が20%上がる、後衛位置にのキャラクタの攻撃力が10%下がる</t>
+    <t>戦闘後獲得するSPが1.5倍になる</t>
+    <rPh sb="0" eb="2">
+      <t>セントウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カクトク</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前衛位置のキャラクタの攻撃力が20%上がる、後衛位置のキャラクタの攻撃力が10%下がる</t>
     <rPh sb="0" eb="2">
       <t>ゼンエイ</t>
     </rPh>
@@ -1698,27 +1654,103 @@
     <rPh sb="24" eb="26">
       <t>イチ</t>
     </rPh>
-    <rPh sb="34" eb="37">
+    <rPh sb="33" eb="36">
       <t>コウゲキリョク</t>
     </rPh>
-    <rPh sb="41" eb="42">
+    <rPh sb="40" eb="41">
       <t>サ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>戦闘後獲得するSPが1.5倍になる</t>
-    <rPh sb="0" eb="2">
-      <t>セントウ</t>
+    <t>味方全員のクリティカル率が5%、クリティカル倍率が50%上がる</t>
+    <rPh sb="0" eb="2">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゼンイン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>バイリツ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>親愛度がプラスの場合、クリティカル率が5%、クリティカル倍率が50%上がる</t>
+    <rPh sb="0" eb="2">
+      <t>シンアイ</t>
     </rPh>
     <rPh sb="2" eb="3">
-      <t>アト</t>
-    </rPh>
-    <rPh sb="3" eb="5">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>親愛度が０以下の場合、クリティカル率が10%、クリティカル倍率が100%上がる</t>
+    <rPh sb="0" eb="2">
+      <t>シンアイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>バイリツ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前衛配置のキャラクターのリロード時間が20%短縮される</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンエイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>タンシュク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>探索時の獲得報酬のレア取得率が上がる</t>
+    <rPh sb="0" eb="3">
+      <t>タンサクジ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
       <t>カクトク</t>
     </rPh>
-    <rPh sb="13" eb="14">
-      <t>バイ</t>
+    <rPh sb="6" eb="8">
+      <t>ホウシュウ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>シュトクリツ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ア</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2146,10 +2178,10 @@
         <v>97</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F2" t="s">
         <v>102</v>
-      </c>
-      <c r="F2" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
@@ -2169,7 +2201,7 @@
         <v>6</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
@@ -2209,7 +2241,7 @@
         <v>30</v>
       </c>
       <c r="F5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.4">
@@ -2226,10 +2258,10 @@
         <v>92</v>
       </c>
       <c r="E6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F6" t="s">
         <v>105</v>
-      </c>
-      <c r="F6" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
@@ -2246,10 +2278,10 @@
         <v>92</v>
       </c>
       <c r="E7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F7" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
@@ -2266,7 +2298,7 @@
         <v>96</v>
       </c>
       <c r="E8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F8" t="s">
         <v>55</v>
@@ -2286,10 +2318,10 @@
         <v>96</v>
       </c>
       <c r="E9" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="F9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.4">
@@ -2306,10 +2338,10 @@
         <v>94</v>
       </c>
       <c r="E10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.4">
@@ -2326,7 +2358,7 @@
         <v>100</v>
       </c>
       <c r="E11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F11" t="s">
         <v>67</v>
@@ -2346,10 +2378,10 @@
         <v>95</v>
       </c>
       <c r="E12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.4">
@@ -2386,7 +2418,7 @@
         <v>96</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F14" t="s">
         <v>28</v>
@@ -2406,10 +2438,10 @@
         <v>96</v>
       </c>
       <c r="E15" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
@@ -2446,7 +2478,7 @@
         <v>96</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F17" t="s">
         <v>34</v>
@@ -2469,7 +2501,7 @@
         <v>45</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.4">
@@ -2506,10 +2538,10 @@
         <v>96</v>
       </c>
       <c r="E20" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.4">
@@ -2526,10 +2558,10 @@
         <v>96</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.4">
@@ -2546,10 +2578,10 @@
         <v>98</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="F22" t="s">
-        <v>55</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.4">
@@ -2566,10 +2598,10 @@
         <v>92</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.4">

--- a/files/tarot/TAROT_data.xlsx
+++ b/files/tarot/TAROT_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\tarot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D3BA1F-C381-4175-AD02-DF2E084E1595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72443B0A-3CC8-4BC4-91A1-4587AEA92877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="780" windowWidth="27990" windowHeight="14415" xr2:uid="{12E5FF72-4590-4256-885D-534FFBE7C063}"/>
+    <workbookView xWindow="1560" yWindow="1305" windowWidth="23745" windowHeight="14895" xr2:uid="{12E5FF72-4590-4256-885D-534FFBE7C063}"/>
   </bookViews>
   <sheets>
     <sheet name="tarot" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="132">
   <si>
     <t>愚者</t>
     <rPh sb="0" eb="2">
@@ -1751,6 +1751,40 @@
     </rPh>
     <rPh sb="15" eb="16">
       <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マップ上の踏破済みのヘクスに、周囲のヘクスのうち一番高いレベル+1の雑魚敵と魔女が生成される。周囲のヘクスに参照できるものがない場合マップ全体からランダムにサンプルを取る。</t>
+    <rPh sb="3" eb="4">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>トウハスミ</t>
+    </rPh>
+    <rPh sb="34" eb="37">
+      <t>ザコテキ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>マジョ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>シュウイ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>サンショウ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="83" eb="84">
+      <t>ト</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1759,7 +1793,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1784,9 +1818,16 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="游ゴシック"/>
-      <family val="2"/>
+      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -1813,7 +1854,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1821,6 +1862,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2143,7 +2187,8 @@
     <col min="2" max="2" width="14.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="61.375" customWidth="1"/>
+    <col min="5" max="5" width="61.375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.4">
@@ -2157,10 +2202,10 @@
       <c r="D1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2180,7 +2225,7 @@
       <c r="E2" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>102</v>
       </c>
     </row>
@@ -2197,7 +2242,7 @@
       <c r="D3" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3" s="2" t="s">
@@ -2217,10 +2262,10 @@
       <c r="D4" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="2" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2237,10 +2282,10 @@
       <c r="D5" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="2" t="s">
         <v>125</v>
       </c>
     </row>
@@ -2257,10 +2302,10 @@
       <c r="D6" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="2" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2277,10 +2322,10 @@
       <c r="D7" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="2" t="s">
         <v>123</v>
       </c>
     </row>
@@ -2297,10 +2342,10 @@
       <c r="D8" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="2" t="s">
         <v>55</v>
       </c>
     </row>
@@ -2317,10 +2362,10 @@
       <c r="D9" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="2" t="s">
         <v>122</v>
       </c>
     </row>
@@ -2337,10 +2382,10 @@
       <c r="D10" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="2" t="s">
         <v>108</v>
       </c>
     </row>
@@ -2357,10 +2402,10 @@
       <c r="D11" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="2" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2377,7 +2422,7 @@
       <c r="D12" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F12" s="2" t="s">
@@ -2397,10 +2442,10 @@
       <c r="D13" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="2" t="s">
         <v>60</v>
       </c>
     </row>
@@ -2420,8 +2465,8 @@
       <c r="E14" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F14" t="s">
-        <v>28</v>
+      <c r="F14" s="3" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
@@ -2437,7 +2482,7 @@
       <c r="D15" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="2" t="s">
         <v>126</v>
       </c>
       <c r="F15" s="2" t="s">
@@ -2457,10 +2502,10 @@
       <c r="D16" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="2" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2480,7 +2525,7 @@
       <c r="E17" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="2" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2497,7 +2542,7 @@
       <c r="D18" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="2" t="s">
         <v>45</v>
       </c>
       <c r="F18" s="2" t="s">
@@ -2517,10 +2562,10 @@
       <c r="D19" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="2" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2537,7 +2582,7 @@
       <c r="D20" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="2" t="s">
         <v>124</v>
       </c>
       <c r="F20" s="2" t="s">
@@ -2580,7 +2625,7 @@
       <c r="E22" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="2" t="s">
         <v>128</v>
       </c>
     </row>

--- a/files/tarot/TAROT_data.xlsx
+++ b/files/tarot/TAROT_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\tarot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72443B0A-3CC8-4BC4-91A1-4587AEA92877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CCBF6F4-7551-4C35-923A-EAC1FBC19F7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1560" yWindow="1305" windowWidth="23745" windowHeight="14895" xr2:uid="{12E5FF72-4590-4256-885D-534FFBE7C063}"/>
   </bookViews>

--- a/files/tarot/TAROT_data.xlsx
+++ b/files/tarot/TAROT_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\tarot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CCBF6F4-7551-4C35-923A-EAC1FBC19F7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C942B739-486D-4B44-B3A6-B80146199827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1305" windowWidth="23745" windowHeight="14895" xr2:uid="{12E5FF72-4590-4256-885D-534FFBE7C063}"/>
+    <workbookView xWindow="300" yWindow="945" windowWidth="23565" windowHeight="14895" xr2:uid="{12E5FF72-4590-4256-885D-534FFBE7C063}"/>
   </bookViews>
   <sheets>
     <sheet name="tarot" sheetId="2" r:id="rId1"/>
